--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B2" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R2" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080580</v>
+        <v>124081374</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548171</v>
+        <v>548107</v>
       </c>
       <c r="R3" t="n">
-        <v>6828435</v>
+        <v>6828598</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R2" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080580</v>
+        <v>124081374</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548171</v>
+        <v>548107</v>
       </c>
       <c r="R3" t="n">
-        <v>6828435</v>
+        <v>6828598</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124234120</v>
+        <v>124231369</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +917,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -953,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548084</v>
+        <v>548094</v>
       </c>
       <c r="R4" t="n">
-        <v>6828623</v>
+        <v>6828562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,17 +1017,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124231369</v>
+        <v>124234120</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,40 +1036,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1077,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548094</v>
+        <v>548084</v>
       </c>
       <c r="R5" t="n">
-        <v>6828562</v>
+        <v>6828623</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,6 +1108,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080580</v>
+        <v>124081374</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548171</v>
+        <v>548107</v>
       </c>
       <c r="R2" t="n">
-        <v>6828435</v>
+        <v>6828598</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R3" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R2" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080580</v>
+        <v>124081374</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548171</v>
+        <v>548107</v>
       </c>
       <c r="R3" t="n">
-        <v>6828435</v>
+        <v>6828598</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124231369</v>
+        <v>124234120</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,40 +917,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -961,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548094</v>
+        <v>548084</v>
       </c>
       <c r="R4" t="n">
-        <v>6828562</v>
+        <v>6828623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,17 +1014,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124234120</v>
+        <v>124231369</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,32 +1033,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1072,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548084</v>
+        <v>548094</v>
       </c>
       <c r="R5" t="n">
-        <v>6828623</v>
+        <v>6828562</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,11 +1113,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124080580</v>
+        <v>124081374</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548171</v>
+        <v>548107</v>
       </c>
       <c r="R2" t="n">
-        <v>6828435</v>
+        <v>6828598</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B3" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R3" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124234120</v>
+        <v>124231369</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,32 +917,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -953,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548084</v>
+        <v>548094</v>
       </c>
       <c r="R4" t="n">
-        <v>6828623</v>
+        <v>6828562</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,11 +997,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,17 +1017,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124231369</v>
+        <v>124234120</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,40 +1036,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1077,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548094</v>
+        <v>548084</v>
       </c>
       <c r="R5" t="n">
-        <v>6828562</v>
+        <v>6828623</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1113,6 +1108,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124231369</v>
+        <v>124234120</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,40 +917,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -961,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548094</v>
+        <v>548084</v>
       </c>
       <c r="R4" t="n">
-        <v>6828562</v>
+        <v>6828623</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,6 +989,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,17 +1014,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124234120</v>
+        <v>124231369</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,32 +1033,40 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1072,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548084</v>
+        <v>548094</v>
       </c>
       <c r="R5" t="n">
-        <v>6828623</v>
+        <v>6828562</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,11 +1113,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett antal plantor invid stammen på en grov gammal gran. Väl skuggade på sydvästra sidan av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124081374</v>
+        <v>124080580</v>
       </c>
       <c r="B2" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548107</v>
+        <v>548171</v>
       </c>
       <c r="R2" t="n">
-        <v>6828598</v>
+        <v>6828435</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124080580</v>
+        <v>124231369</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,27 +815,31 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ön 1:1 16, Hls</t>
+          <t>Ön 1:1, Stormoberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548171</v>
+        <v>548094</v>
       </c>
       <c r="R3" t="n">
-        <v>6828435</v>
+        <v>6828562</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,12 +887,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -908,12 +902,7 @@
         <v>124234120</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,66 +1010,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124231369</v>
+        <v>124081374</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ön 1:1, Stormoberget, Hls</t>
+          <t>Ön 1:1 16, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548094</v>
+        <v>548107</v>
       </c>
       <c r="R5" t="n">
-        <v>6828562</v>
+        <v>6828598</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,12 +1108,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 17707-2025 artfynd.xlsx
+++ b/artfynd/A 17707-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124080580</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124231369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124234120</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,8 +1137,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>